--- a/artfynd/A 29500-2025 artfynd.xlsx
+++ b/artfynd/A 29500-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>126590390</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29500-2025 artfynd.xlsx
+++ b/artfynd/A 29500-2025 artfynd.xlsx
@@ -788,7 +788,7 @@
         <v>126590390</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29500-2025 artfynd.xlsx
+++ b/artfynd/A 29500-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126590391</v>
       </c>
       <c r="B2" t="n">
-        <v>57578</v>
+        <v>57637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,14 +781,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>126590390</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -878,7 +882,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
